--- a/output/extracted_urls/motortrend/motortrend_urls.xlsx
+++ b/output/extracted_urls/motortrend/motortrend_urls.xlsx
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Body is a performance-test ride report with speed figures and impressions, but no substantive engineering or R&amp;D analysis.</t>
+          <t>Mostly a performance first-drive narrative with lap impressions and 0-60 timing, not substantive engineering or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mostly a performance road-test with specs and comparisons; little engineering or R&amp;D analysis beyond basic engine and gearing details.</t>
+          <t>Mostly a performance road-test/review with specs and comparisons, not substantive engineering or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Body is just a consumer list of fuel-economy picks with EPA mileage rankings, not engineering or R&amp;D content.</t>
+          <t>Body is a consumer list of fuel-efficient compact cars with EPA mileage figures, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Body is a subjective style roundup with no substantive engineering or R&amp;D detail beyond brief generic EV styling remarks.</t>
+          <t>A subjective style roundup with no substantive engineering or R&amp;D content in the body.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mostly a safeties listicle with awards and model rankings, not substantive engineering or validation detail in the body.</t>
+          <t>Mostly a safety-awards list with no substantive engineering or validation analysis in the body.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A list of safe small SUVs with crash-test ratings, but no substantive engineering or R&amp;D analysis beyond awards and rankings.</t>
+          <t>A listicle of safety-rated SUVs with no substantive engineering or validation detail beyond award criteria.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Body is a promo-style e-bike episode with little engineering detail beyond buzzwords like pedal-by-wire.</t>
+          <t>Body is mostly a podcast intro and product teaser about an e-bike, with no substantive automotive engineering or validation detail.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mostly a strategy/interview piece about sales goals and model rollout, with little substantive engineering detail beyond broad platform mentions.</t>
+          <t>Mostly a strategy-and-sales interview with launch plans; the body gives little engineering depth beyond broad mentions of new platforms and AI tech.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Body is a consumer value roundup of luxury-feel SUVs, with no engineering, validation, or R&amp;D substance.</t>
+          <t>Body is a consumer value roundup with no engineering or R&amp;D substance, just luxury-feel rankings and pricing context.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mostly a business/manufacturing update about ending ID4 production and plant reallocation, with no substantive engineering or validation detail.</t>
+          <t>Mostly a business/production shift story with no substantive engineering, validation, or platform detail in the body.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Body is mostly a police-vehicle certification and equipment overview, with little engineering depth beyond basic hardware specs and no real R&amp;D or validation insight.</t>
+          <t>Describes police-duty hardware and validation, but the body is mostly a vehicle certification/spec overview with little engineering depth.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body has substantial engineering detail on 800V architecture, battery chemistry, two-speed drive unit, and charging/regen limits.</t>
+          <t>Body gives concrete engineering details on 800V architecture, battery chemistry, two-speed transaxle, and charging/regen performance changes.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>The body explains a specific cold-start emissions hardware architecture, including burner control, air-fuel ratio, sensors, and thermal strategy.</t>
+          <t>Body gives concrete emissions-control engineering details on cold-start catalyst heating, burner architecture, and 12V/thermal implications.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mostly a consumer yearlong review with specs and subjective impressions, not substantive engineering or validation analysis.</t>
+          <t>Mostly a first-impressions yearlong review of a production SUV, with specs and comfort notes but little engineering or validation substance.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Body is a cost-and-ownership complaint about windshield damage and recalibration, with no meaningful engineering or R&amp;D analysis.</t>
+          <t>Body is a cost-and-ownership complaint about repeated windshield damage and repair bills, with no meaningful engineering analysis.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Body has some engineering content on hybrids, body-on-frame platforms, and battery cost work, but it is mostly product-planning and lineup strategy.</t>
+          <t>Contains some platform and hybrid/battery planning, but the body is mostly a product lineup and market strategy summary with limited engineering detail.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Body is about farm biogas liquefaction and fuel production, with little direct automotive engineering, validation, or vehicle-system detail.</t>
+          <t>Body explains a renewable methane/liquefaction process for farm biogas, but it is energy-tech rather than automotive engineering with no vehicle, validation, or platform implications.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>The body discusses SDV software architecture, fragmented integration, pre-certified platforms, and engineering risks like recalls and updateability.</t>
+          <t>Body discusses SDV software architecture, fragmented integration, pre-certified platform design, and update/safety implications for OEM and Tier 1 engineering teams.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mostly a performance review of a modified Mustang; it gives setup details but little engineering depth beyond horsepower, suspension, and tire fitment.</t>
+          <t>Mostly a performance review of a tuned Mustang; the body lacks substantive engineering or R&amp;D analysis beyond basic mod and power specs.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mostly pricing and trim/package news with only brief technical mentions; no substantive engineering or validation discussion in the body.</t>
+          <t>Mostly pricing and trim/package news, with only brief mentions of LS6, AWD, and brakes and no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mostly a trim/farewell announcement with pricing and cosmetic changes, not substantive engineering or R&amp;D content.</t>
+          <t>Mostly a trim-package farewell and pricing/news item, with no substantive engineering or R&amp;D detail in the body.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Body is a consumer roundup focused on fuel savings and price, with no engineering or R&amp;D substance.</t>
+          <t>Body is a consumer listicle about affordable hybrids and fuel savings, with no engineering, validation, or architecture detail.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Body is mostly opinionated lessons from a long-term review, with limited engineering detail on the EREV architecture itself.</t>
+          <t>Body is mostly editorial advice on a future EREV with little concrete engineering detail, validation data, or system analysis.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mostly a model-first car announcement with specs and styling; little engineering depth beyond sharing suspension and lightweight parts.</t>
+          <t>Mostly a feature/launch writeup with specs and lightweight parts, but no real engineering, validation, or R&amp;D analysis.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Body is purely a cosmetic special-edition description with no engineering, validation, or platform changes.</t>
+          <t>Body is a cosmetic retro trim overview with no engineering, validation, or technical change beyond styling.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mostly an auction/charity feature; body is mainly vehicle specs and event details, with little engineering or R&amp;D insight.</t>
+          <t>Contains some vehicle engineering specs, but the body is mostly an auction/charity feature and general vehicle description, not substantive R&amp;D or validation content.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mostly trade-policy and market-share discussion; the body lacks engineering, validation, or vehicle-development substance.</t>
+          <t>Mostly trade and market-share discussion; the body lacks engineering, validation, or vehicle-development substance.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Body is a consumer-style overview of classic EV conversions with general benefits and cost/performance comments, not engineering-focused R&amp;D analysis.</t>
+          <t>Body is mostly enthusiast commentary on classic EV conversions, with only broad mentions of cost, range, weight, and torque but no substantive engineering depth.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Mostly naming and product-planning discussion; the body gives only platform mentions with no meaningful engineering detail or R&amp;D substance.</t>
+          <t>Body is mainly a naming/debate piece, with only brief mention of a new body-on-frame platform and no substantive engineering detail.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>The body gives concrete powertrain architecture and efficiency-design details—pushrod layout, two-valve monoblock, roller bearings, offset crank, and electric auxiliaries—relevant to hybrid engine engineering.</t>
+          <t>The body gives concrete powertrain architecture and efficiency-design details—pushrod monoblock, dual motor-generators, roller bearings, offset crank, and electric auxiliaries—useful for engineering evaluation.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>The body gives substantive engineering-organization detail about integrating product development, design, engineering, manufacturing, and the UEV platform to speed EV/software-defined vehicle development.</t>
+          <t>Body gives concrete engineering/industrialization details on Ford’s EV and software-defined vehicle restructuring, platform rollout, and integrated development/manufacturing changes.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
